--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="Rbeb90af72bf54e6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R7f232ddd0ca84a2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Rd313adb4b08a485b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Rb1fd84d1e3794a1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R5cf0b65fd55c4b1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Redff640eccd0470f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R8f19eb0d054740d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R5a5304002f7e4914"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Rd6ad6f58406b4a6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R7d752a8f92924e32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="Rfa0fcc73b4a74d07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rb01074c44e464a50"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -337,7 +337,7 @@
         <x:color rgb="FF1B5E20"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF3E4"/>
         </x:patternFill>
       </x:fill>
@@ -348,7 +348,7 @@
         <x:color rgb="FF7A4F00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0C2"/>
         </x:patternFill>
       </x:fill>
@@ -359,7 +359,7 @@
         <x:color rgb="FF8B1A1A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFADBD8"/>
         </x:patternFill>
       </x:fill>
@@ -370,7 +370,7 @@
         <x:color rgb="FF1B5E20"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF3E4"/>
         </x:patternFill>
       </x:fill>
@@ -381,7 +381,7 @@
         <x:color rgb="FF7A4F00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0C2"/>
         </x:patternFill>
       </x:fill>
@@ -392,7 +392,7 @@
         <x:color rgb="FF8B1A1A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFADBD8"/>
         </x:patternFill>
       </x:fill>
@@ -403,7 +403,7 @@
         <x:color rgb="FF1B5E20"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF3E4"/>
         </x:patternFill>
       </x:fill>
@@ -414,7 +414,7 @@
         <x:color rgb="FF8B1A1A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFADBD8"/>
         </x:patternFill>
       </x:fill>
@@ -425,7 +425,7 @@
         <x:color rgb="FF7A4F00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0C2"/>
         </x:patternFill>
       </x:fill>
@@ -870,7 +870,7 @@
       </x:c>
       <x:c r="B12" s="28" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành")+COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành có lỗi")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -879,7 +879,7 @@
       </x:c>
       <x:c r="B13" s="29" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Chưa chạy")</x:f>
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1138,7 +1138,7 @@
       </x:c>
       <x:c r="N4" s="36" t="str">
         <x:f>'CRAWL_LOG'!B4</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="O4" s="36" t="str">
         <x:v>Supplementary panel</x:v>
@@ -6252,7 +6252,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28f642a08bc944d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09d47eb230844500"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6444,29 +6444,54 @@
         <x:v>46258</x:v>
       </x:c>
       <x:c r="B4" s="36" t="str">
-        <x:v>Chưa chạy</x:v>
-      </x:c>
-      <x:c r="C4" s="36"/>
-      <x:c r="D4" s="44"/>
-      <x:c r="E4" s="44"/>
-      <x:c r="F4" s="46" t="str">
+        <x:v>Hoàn thành</x:v>
+      </x:c>
+      <x:c r="C4" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D4" s="44" t="n">
+        <x:v>46258.02627314815</x:v>
+      </x:c>
+      <x:c r="E4" s="44" t="n">
+        <x:v>46258.71729166667</x:v>
+      </x:c>
+      <x:c r="F4" s="46" t="n">
         <x:f>IF(OR(D4="",E4=""),"",24*(E4-D4))</x:f>
-      </x:c>
-      <x:c r="G4" s="48"/>
-      <x:c r="H4" s="48"/>
-      <x:c r="I4" s="48"/>
-      <x:c r="J4" s="48"/>
-      <x:c r="K4" s="48"/>
-      <x:c r="L4" s="48"/>
-      <x:c r="M4" s="48"/>
-      <x:c r="N4" s="48"/>
+        <x:v>16.584444444451947</x:v>
+      </x:c>
+      <x:c r="G4" s="48" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="H4" s="48" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="I4" s="48" t="n">
+        <x:v>1525</x:v>
+      </x:c>
+      <x:c r="J4" s="48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K4" s="48" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="L4" s="48" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M4" s="48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N4" s="48" t="n">
+        <x:v>13709</x:v>
+      </x:c>
       <x:c r="O4" s="48" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P4" s="36" t="str">
         <x:v>vps</x:v>
       </x:c>
-      <x:c r="Q4" s="36"/>
+      <x:c r="Q4" s="36" t="str">
+        <x:v>Manual run #1 trên deploy; đúng 5 ngày VPS; artifact không lưu; scraper 2.3.0</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="40" t="n">
@@ -9327,7 +9352,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3aab06b98c8459c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97f8dc1c92f84c01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14461,7 +14486,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f0e6225d7c44f9d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9c437c2d964156"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14674,7 +14699,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d9c47c197014126"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab8c9adacb094778"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14821,7 +14846,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51a20782be084027"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re00a31487412436d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R8f19eb0d054740d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R5a5304002f7e4914"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Rd6ad6f58406b4a6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R7d752a8f92924e32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="Rfa0fcc73b4a74d07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rb01074c44e464a50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R0dbd5cb59e4548dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R8a447dbed3714967"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Rce3a659a91fc47b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R0ce4c2f0d3414914"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R25c6fe9524974097"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rbe6d7e4bcbd1415f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -879,7 +879,7 @@
       </x:c>
       <x:c r="B13" s="29" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Chưa chạy")</x:f>
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1190,7 +1190,7 @@
       </x:c>
       <x:c r="N5" s="37" t="str">
         <x:f>'CRAWL_LOG'!B5</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Đang chạy</x:v>
       </x:c>
       <x:c r="O5" s="37" t="str">
         <x:v>Supplementary panel</x:v>
@@ -6252,7 +6252,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09d47eb230844500"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cf266cd2d5d40f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6498,10 +6498,14 @@
         <x:v>46259</x:v>
       </x:c>
       <x:c r="B5" s="37" t="str">
-        <x:v>Chưa chạy</x:v>
-      </x:c>
-      <x:c r="C5" s="37"/>
-      <x:c r="D5" s="45"/>
+        <x:v>Đang chạy</x:v>
+      </x:c>
+      <x:c r="C5" s="37" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D5" s="45" t="n">
+        <x:v>46259.03542824074</x:v>
+      </x:c>
       <x:c r="E5" s="45"/>
       <x:c r="F5" s="47" t="str">
         <x:f>IF(OR(D5="",E5=""),"",24*(E5-D5))</x:f>
@@ -6520,7 +6524,9 @@
       <x:c r="P5" s="37" t="str">
         <x:v>vps</x:v>
       </x:c>
-      <x:c r="Q5" s="37"/>
+      <x:c r="Q5" s="37" t="str">
+        <x:v>Scheduled VPS crawl đã tạo trên deploy; artifact không lưu</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="39" t="n">
@@ -9352,7 +9358,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97f8dc1c92f84c01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98a7053bfa2c4e7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14486,7 +14492,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9c437c2d964156"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7623d3832d0649b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14699,7 +14705,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab8c9adacb094778"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2798b1ee81484afe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14846,7 +14852,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re00a31487412436d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c54a50193ed43be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R0dbd5cb59e4548dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R8a447dbed3714967"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Rce3a659a91fc47b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R0ce4c2f0d3414914"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R25c6fe9524974097"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rbe6d7e4bcbd1415f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="Raae87a36ee704117"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R32c78b455f5b45af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Rf4a727907fcf4292"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Rd7f1d909fc6148fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R314644efeffc4bff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Ra99a1097832f48d1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -870,7 +870,7 @@
       </x:c>
       <x:c r="B12" s="28" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành")+COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành có lỗi")</x:f>
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -879,7 +879,7 @@
       </x:c>
       <x:c r="B13" s="29" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Chưa chạy")</x:f>
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1190,7 +1190,7 @@
       </x:c>
       <x:c r="N5" s="37" t="str">
         <x:f>'CRAWL_LOG'!B5</x:f>
-        <x:v>Đang chạy</x:v>
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="O5" s="37" t="str">
         <x:v>Supplementary panel</x:v>
@@ -1242,7 +1242,7 @@
       </x:c>
       <x:c r="N6" s="36" t="str">
         <x:f>'CRAWL_LOG'!B6</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="O6" s="36" t="str">
         <x:v>Supplementary panel</x:v>
@@ -6252,7 +6252,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cf266cd2d5d40f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb82581717883419d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6498,7 +6498,7 @@
         <x:v>46259</x:v>
       </x:c>
       <x:c r="B5" s="37" t="str">
-        <x:v>Đang chạy</x:v>
+        <x:v>Hoàn thành</x:v>
       </x:c>
       <x:c r="C5" s="37" t="str">
         <x:v>2</x:v>
@@ -6506,18 +6506,37 @@
       <x:c r="D5" s="45" t="n">
         <x:v>46259.03542824074</x:v>
       </x:c>
-      <x:c r="E5" s="45"/>
-      <x:c r="F5" s="47" t="str">
+      <x:c r="E5" s="45" t="n">
+        <x:v>46259.75431712963</x:v>
+      </x:c>
+      <x:c r="F5" s="47" t="n">
         <x:f>IF(OR(D5="",E5=""),"",24*(E5-D5))</x:f>
-      </x:c>
-      <x:c r="G5" s="49"/>
-      <x:c r="H5" s="49"/>
-      <x:c r="I5" s="49"/>
-      <x:c r="J5" s="49"/>
-      <x:c r="K5" s="49"/>
-      <x:c r="L5" s="49"/>
-      <x:c r="M5" s="49"/>
-      <x:c r="N5" s="49"/>
+        <x:v>17.253333333239425</x:v>
+      </x:c>
+      <x:c r="G5" s="49" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="H5" s="49" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="I5" s="49" t="n">
+        <x:v>1515</x:v>
+      </x:c>
+      <x:c r="J5" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K5" s="49" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="L5" s="49" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M5" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N5" s="49" t="n">
+        <x:v>13327</x:v>
+      </x:c>
       <x:c r="O5" s="49" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -6525,7 +6544,7 @@
         <x:v>vps</x:v>
       </x:c>
       <x:c r="Q5" s="37" t="str">
-        <x:v>Scheduled VPS crawl đã tạo trên deploy; artifact không lưu</x:v>
+        <x:v>Run ID 2; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal API status completed</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6533,29 +6552,53 @@
         <x:v>46260</x:v>
       </x:c>
       <x:c r="B6" s="36" t="str">
-        <x:v>Chưa chạy</x:v>
-      </x:c>
-      <x:c r="C6" s="36"/>
-      <x:c r="D6" s="44"/>
-      <x:c r="E6" s="44"/>
-      <x:c r="F6" s="46" t="str">
-        <x:f>IF(OR(D6="",E6=""),"",24*(E6-D6))</x:f>
-      </x:c>
-      <x:c r="G6" s="48"/>
-      <x:c r="H6" s="48"/>
-      <x:c r="I6" s="48"/>
-      <x:c r="J6" s="48"/>
-      <x:c r="K6" s="48"/>
-      <x:c r="L6" s="48"/>
-      <x:c r="M6" s="48"/>
-      <x:c r="N6" s="48"/>
+        <x:v>Hoàn thành</x:v>
+      </x:c>
+      <x:c r="C6" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D6" s="44" t="n">
+        <x:v>46260.0284375</x:v>
+      </x:c>
+      <x:c r="E6" s="44" t="n">
+        <x:v>46260.77434027778</x:v>
+      </x:c>
+      <x:c r="F6" s="46" t="n">
+        <x:v>17.901666666666667</x:v>
+      </x:c>
+      <x:c r="G6" s="48" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="H6" s="48" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="I6" s="48" t="n">
+        <x:v>1506</x:v>
+      </x:c>
+      <x:c r="J6" s="48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="48" t="n">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="L6" s="48" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M6" s="48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N6" s="48" t="n">
+        <x:v>13245</x:v>
+      </x:c>
       <x:c r="O6" s="48" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P6" s="36" t="str">
         <x:v>vps</x:v>
       </x:c>
-      <x:c r="Q6" s="36"/>
+      <x:c r="Q6" s="36" t="str">
+        <x:v>Run ID 3; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal API status completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="40" t="n">
@@ -9358,7 +9401,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98a7053bfa2c4e7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25d29b79f2244d17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14492,7 +14535,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7623d3832d0649b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb78853e0950942b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14705,7 +14748,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2798b1ee81484afe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec87759633cc4bba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14852,7 +14895,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c54a50193ed43be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra890dd0206d14e18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="Raae87a36ee704117"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R32c78b455f5b45af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Rf4a727907fcf4292"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Rd7f1d909fc6148fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R314644efeffc4bff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Ra99a1097832f48d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R9fad5770e0804b9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="Rb07c2d44e2794caf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R0cea5d9bf18b4a10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R15ec0895834e44bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R798cbe464ec445a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="R9dd1d88522fb4498"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -870,7 +870,7 @@
       </x:c>
       <x:c r="B12" s="28" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành")+COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành có lỗi")</x:f>
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -879,7 +879,7 @@
       </x:c>
       <x:c r="B13" s="29" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Chưa chạy")</x:f>
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1294,7 +1294,7 @@
       </x:c>
       <x:c r="N7" s="37" t="str">
         <x:f>'CRAWL_LOG'!B7</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="O7" s="37" t="str">
         <x:v>Supplementary panel</x:v>
@@ -1346,7 +1346,7 @@
       </x:c>
       <x:c r="N8" s="36" t="str">
         <x:f>'CRAWL_LOG'!B8</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Đang chạy</x:v>
       </x:c>
       <x:c r="O8" s="36" t="str">
         <x:v>Supplementary panel</x:v>
@@ -6252,7 +6252,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb82581717883419d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe2114b7253e4756"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6605,39 +6605,67 @@
         <x:v>46261</x:v>
       </x:c>
       <x:c r="B7" s="37" t="str">
-        <x:v>Chưa chạy</x:v>
-      </x:c>
-      <x:c r="C7" s="37"/>
-      <x:c r="D7" s="45"/>
-      <x:c r="E7" s="45"/>
-      <x:c r="F7" s="47" t="str">
-        <x:f>IF(OR(D7="",E7=""),"",24*(E7-D7))</x:f>
-      </x:c>
-      <x:c r="G7" s="49"/>
-      <x:c r="H7" s="49"/>
-      <x:c r="I7" s="49"/>
-      <x:c r="J7" s="49"/>
-      <x:c r="K7" s="49"/>
-      <x:c r="L7" s="49"/>
-      <x:c r="M7" s="49"/>
-      <x:c r="N7" s="49"/>
+        <x:v>Hoàn thành có lỗi</x:v>
+      </x:c>
+      <x:c r="C7" s="37" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D7" s="45" t="n">
+        <x:v>46261.02307870371</x:v>
+      </x:c>
+      <x:c r="E7" s="45" t="n">
+        <x:v>46261.93287037037</x:v>
+      </x:c>
+      <x:c r="F7" s="47" t="n">
+        <x:v>21.834999999962747</x:v>
+      </x:c>
+      <x:c r="G7" s="49" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="H7" s="49" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="I7" s="49" t="n">
+        <x:v>1544</x:v>
+      </x:c>
+      <x:c r="J7" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="49" t="n">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="L7" s="49" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="M7" s="49" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N7" s="49" t="n">
+        <x:v>14080</x:v>
+      </x:c>
       <x:c r="O7" s="49" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P7" s="37" t="str">
         <x:v>vps</x:v>
       </x:c>
-      <x:c r="Q7" s="37"/>
+      <x:c r="Q7" s="37" t="str">
+        <x:v>Run ID 4; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal API status completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="39" t="n">
         <x:v>46262</x:v>
       </x:c>
       <x:c r="B8" s="36" t="str">
-        <x:v>Chưa chạy</x:v>
-      </x:c>
-      <x:c r="C8" s="36"/>
-      <x:c r="D8" s="44"/>
+        <x:v>Đang chạy</x:v>
+      </x:c>
+      <x:c r="C8" s="36" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D8" s="44" t="n">
+        <x:v>46262.037210648145</x:v>
+      </x:c>
       <x:c r="E8" s="44"/>
       <x:c r="F8" s="46" t="str">
         <x:f>IF(OR(D8="",E8=""),"",24*(E8-D8))</x:f>
@@ -6656,7 +6684,9 @@
       <x:c r="P8" s="36" t="str">
         <x:v>vps</x:v>
       </x:c>
-      <x:c r="Q8" s="36"/>
+      <x:c r="Q8" s="36" t="str">
+        <x:v>Scheduled VPS crawl đã tạo trên deploy; artifact không lưu</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="40" t="n">
@@ -9401,7 +9431,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25d29b79f2244d17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbe79912d93c4ba8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14535,7 +14565,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb78853e0950942b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R609b97d4b2914c3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14748,7 +14778,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec87759633cc4bba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref66c578c56444d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14895,7 +14925,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra890dd0206d14e18"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f9a1b4610b045c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R9fad5770e0804b9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="Rb07c2d44e2794caf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R0cea5d9bf18b4a10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R15ec0895834e44bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R798cbe464ec445a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="R9dd1d88522fb4498"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="Rc1dc9e12264f40be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R32f8039ed40e4625"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Ra6f2476aafa649ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R3fc8b614c3044ce9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="Rfc63d1c9ce8f4fd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rbeb9bf81e8824e77"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -870,7 +870,7 @@
       </x:c>
       <x:c r="B12" s="28" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành")+COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành có lỗi")</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1346,7 +1346,7 @@
       </x:c>
       <x:c r="N8" s="36" t="str">
         <x:f>'CRAWL_LOG'!B8</x:f>
-        <x:v>Đang chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="O8" s="36" t="str">
         <x:v>Supplementary panel</x:v>
@@ -6252,7 +6252,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe2114b7253e4756"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R607d51020c0c4995"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6658,26 +6658,44 @@
         <x:v>46262</x:v>
       </x:c>
       <x:c r="B8" s="36" t="str">
-        <x:v>Đang chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="C8" s="36" t="str">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D8" s="44" t="n">
-        <x:v>46262.037210648145</x:v>
-      </x:c>
-      <x:c r="E8" s="44"/>
-      <x:c r="F8" s="46" t="str">
-        <x:f>IF(OR(D8="",E8=""),"",24*(E8-D8))</x:f>
-      </x:c>
-      <x:c r="G8" s="48"/>
-      <x:c r="H8" s="48"/>
-      <x:c r="I8" s="48"/>
-      <x:c r="J8" s="48"/>
-      <x:c r="K8" s="48"/>
-      <x:c r="L8" s="48"/>
-      <x:c r="M8" s="48"/>
-      <x:c r="N8" s="48"/>
+        <x:v>46262.03721064815</x:v>
+      </x:c>
+      <x:c r="E8" s="44" t="n">
+        <x:v>46262.8571412037</x:v>
+      </x:c>
+      <x:c r="F8" s="46" t="n">
+        <x:v>19.678333333333335</x:v>
+      </x:c>
+      <x:c r="G8" s="48" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="H8" s="48" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="I8" s="48" t="n">
+        <x:v>1495</x:v>
+      </x:c>
+      <x:c r="J8" s="48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" s="48" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="L8" s="48" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="M8" s="48" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N8" s="48" t="n">
+        <x:v>13016</x:v>
+      </x:c>
       <x:c r="O8" s="48" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -6685,7 +6703,7 @@
         <x:v>vps</x:v>
       </x:c>
       <x:c r="Q8" s="36" t="str">
-        <x:v>Scheduled VPS crawl đã tạo trên deploy; artifact không lưu</x:v>
+        <x:v>Run ID 5; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal completed</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -9431,7 +9449,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbe79912d93c4ba8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R444403d6eaea4d66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14565,7 +14583,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R609b97d4b2914c3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6feeab3e1d9045fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14778,7 +14796,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref66c578c56444d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf21e2f965bd42a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14925,7 +14943,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f9a1b4610b045c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3480da1a74464cc0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="Rc1dc9e12264f40be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R32f8039ed40e4625"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Ra6f2476aafa649ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R3fc8b614c3044ce9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="Rfc63d1c9ce8f4fd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rbeb9bf81e8824e77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R139c6f862e0444df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R10e901d2ae4a413f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R08a77d425e4e42aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Re35ad5004069452e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R960c607d8ff745a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="R1f9f1bd7537449f8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -870,7 +870,7 @@
       </x:c>
       <x:c r="B12" s="28" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành")+COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành có lỗi")</x:f>
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -879,7 +879,7 @@
       </x:c>
       <x:c r="B13" s="29" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Chưa chạy")</x:f>
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1398,7 +1398,7 @@
       </x:c>
       <x:c r="N9" s="37" t="str">
         <x:f>'CRAWL_LOG'!B9</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="O9" s="37" t="str">
         <x:v>Supplementary panel</x:v>
@@ -6252,7 +6252,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R607d51020c0c4995"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e83ff52f9d84b23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6711,29 +6711,53 @@
         <x:v>46263</x:v>
       </x:c>
       <x:c r="B9" s="37" t="str">
-        <x:v>Chưa chạy</x:v>
-      </x:c>
-      <x:c r="C9" s="37"/>
-      <x:c r="D9" s="45"/>
-      <x:c r="E9" s="45"/>
-      <x:c r="F9" s="47" t="str">
-        <x:f>IF(OR(D9="",E9=""),"",24*(E9-D9))</x:f>
-      </x:c>
-      <x:c r="G9" s="49"/>
-      <x:c r="H9" s="49"/>
-      <x:c r="I9" s="49"/>
-      <x:c r="J9" s="49"/>
-      <x:c r="K9" s="49"/>
-      <x:c r="L9" s="49"/>
-      <x:c r="M9" s="49"/>
-      <x:c r="N9" s="49"/>
+        <x:v>Hoàn thành có lỗi</x:v>
+      </x:c>
+      <x:c r="C9" s="37" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D9" s="45" t="n">
+        <x:v>46262.732395833336</x:v>
+      </x:c>
+      <x:c r="E9" s="45" t="n">
+        <x:v>46263.909166666665</x:v>
+      </x:c>
+      <x:c r="F9" s="47" t="n">
+        <x:v>28.2424999998766</x:v>
+      </x:c>
+      <x:c r="G9" s="49" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="H9" s="49" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="I9" s="49" t="n">
+        <x:v>1569</x:v>
+      </x:c>
+      <x:c r="J9" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K9" s="49" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="L9" s="49" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="M9" s="49" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N9" s="49" t="n">
+        <x:v>15195</x:v>
+      </x:c>
       <x:c r="O9" s="49" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P9" s="37" t="str">
         <x:v>vps</x:v>
       </x:c>
-      <x:c r="Q9" s="37"/>
+      <x:c r="Q9" s="37" t="str">
+        <x:v>Run ID 6; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal API status completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="39" t="n">
@@ -9449,7 +9473,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R444403d6eaea4d66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98bd102d09374818"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14583,7 +14607,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6feeab3e1d9045fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c0a2c4cb27f4b86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14796,7 +14820,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf21e2f965bd42a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb74f12d2fad6403a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14943,7 +14967,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3480da1a74464cc0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b1459813fd944a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R139c6f862e0444df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R10e901d2ae4a413f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R08a77d425e4e42aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Re35ad5004069452e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R960c607d8ff745a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="R1f9f1bd7537449f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R97300a049eca4b36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R034ce9f76e0e4c3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R1fb5c0610865419b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Rbc7f2860a3d64463"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R6a3fccb9895d4c93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="R79b6d5ae80884c43"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -870,7 +870,7 @@
       </x:c>
       <x:c r="B12" s="28" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành")+COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành có lỗi")</x:f>
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -879,7 +879,7 @@
       </x:c>
       <x:c r="B13" s="29" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Chưa chạy")</x:f>
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1450,7 +1450,7 @@
       </x:c>
       <x:c r="N10" s="36" t="str">
         <x:f>'CRAWL_LOG'!B10</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="O10" s="36" t="str">
         <x:v>Supplementary panel</x:v>
@@ -6252,7 +6252,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e83ff52f9d84b23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3e6a6189afd4f97"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6764,29 +6764,53 @@
         <x:v>46264</x:v>
       </x:c>
       <x:c r="B10" s="36" t="str">
-        <x:v>Chưa chạy</x:v>
-      </x:c>
-      <x:c r="C10" s="36"/>
-      <x:c r="D10" s="44"/>
-      <x:c r="E10" s="44"/>
-      <x:c r="F10" s="46" t="str">
-        <x:f>IF(OR(D10="",E10=""),"",24*(E10-D10))</x:f>
-      </x:c>
-      <x:c r="G10" s="48"/>
-      <x:c r="H10" s="48"/>
-      <x:c r="I10" s="48"/>
-      <x:c r="J10" s="48"/>
-      <x:c r="K10" s="48"/>
-      <x:c r="L10" s="48"/>
-      <x:c r="M10" s="48"/>
-      <x:c r="N10" s="48"/>
+        <x:v>Hoàn thành có lỗi</x:v>
+      </x:c>
+      <x:c r="C10" s="36" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D10" s="44" t="n">
+        <x:v>46263.73232638889</x:v>
+      </x:c>
+      <x:c r="E10" s="44" t="n">
+        <x:v>46264.507881944446</x:v>
+      </x:c>
+      <x:c r="F10" s="46" t="n">
+        <x:v>18.613333333333333</x:v>
+      </x:c>
+      <x:c r="G10" s="48" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="H10" s="48" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="I10" s="48" t="n">
+        <x:v>1475</x:v>
+      </x:c>
+      <x:c r="J10" s="48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" s="48" t="n">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="L10" s="48" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="M10" s="48" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N10" s="48" t="n">
+        <x:v>12987</x:v>
+      </x:c>
       <x:c r="O10" s="48" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P10" s="36" t="str">
         <x:v>vps</x:v>
       </x:c>
-      <x:c r="Q10" s="36"/>
+      <x:c r="Q10" s="36" t="str">
+        <x:v>Run ID 7; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal API status completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="40" t="n">
@@ -9473,7 +9497,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98bd102d09374818"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re148f00eb39d4c11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14607,7 +14631,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c0a2c4cb27f4b86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc74bc56ed77f4b71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14820,7 +14844,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb74f12d2fad6403a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5639f8d259ec42b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14967,7 +14991,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b1459813fd944a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92a93dda4e4b4450"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R97300a049eca4b36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R034ce9f76e0e4c3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R1fb5c0610865419b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Rbc7f2860a3d64463"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R6a3fccb9895d4c93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="R79b6d5ae80884c43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="Rb9e004f631a34147"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R3f466e7fe169444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R08302848a24e4442"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Rc0730c2bb1374cbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="Rd27f8aec09a1411e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="R84456051bd3141c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -870,7 +870,7 @@
       </x:c>
       <x:c r="B12" s="28" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành")+COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành có lỗi")</x:f>
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -879,7 +879,7 @@
       </x:c>
       <x:c r="B13" s="29" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Chưa chạy")</x:f>
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1502,7 +1502,7 @@
       </x:c>
       <x:c r="N11" s="37" t="str">
         <x:f>'CRAWL_LOG'!B11</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="O11" s="37" t="str">
         <x:v>Supplementary panel</x:v>
@@ -6252,7 +6252,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3e6a6189afd4f97"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9d6dd3fb2ad4d7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6817,29 +6817,53 @@
         <x:v>46265</x:v>
       </x:c>
       <x:c r="B11" s="37" t="str">
-        <x:v>Chưa chạy</x:v>
-      </x:c>
-      <x:c r="C11" s="37"/>
-      <x:c r="D11" s="45"/>
-      <x:c r="E11" s="45"/>
-      <x:c r="F11" s="47" t="str">
-        <x:f>IF(OR(D11="",E11=""),"",24*(E11-D11))</x:f>
-      </x:c>
-      <x:c r="G11" s="49"/>
-      <x:c r="H11" s="49"/>
-      <x:c r="I11" s="49"/>
-      <x:c r="J11" s="49"/>
-      <x:c r="K11" s="49"/>
-      <x:c r="L11" s="49"/>
-      <x:c r="M11" s="49"/>
-      <x:c r="N11" s="49"/>
+        <x:v>Hoàn thành có lỗi</x:v>
+      </x:c>
+      <x:c r="C11" s="37" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D11" s="45" t="n">
+        <x:v>46264.73168981481</x:v>
+      </x:c>
+      <x:c r="E11" s="45" t="n">
+        <x:v>46265.57034722222</x:v>
+      </x:c>
+      <x:c r="F11" s="47" t="n">
+        <x:v>20.127777777777776</x:v>
+      </x:c>
+      <x:c r="G11" s="49" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="H11" s="49" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="I11" s="49" t="n">
+        <x:v>1569</x:v>
+      </x:c>
+      <x:c r="J11" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" s="49" t="n">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="L11" s="49" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="M11" s="49" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N11" s="49" t="n">
+        <x:v>15130</x:v>
+      </x:c>
       <x:c r="O11" s="49" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P11" s="37" t="str">
         <x:v>vps</x:v>
       </x:c>
-      <x:c r="Q11" s="37"/>
+      <x:c r="Q11" s="37" t="str">
+        <x:v>Run ID 8; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal API completed; items pagination 1775; saved_options_count 15130.</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="39" t="n">
@@ -9497,7 +9521,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re148f00eb39d4c11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57fd285de49141ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14631,7 +14655,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc74bc56ed77f4b71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R477b4f962e1f4e93"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14844,7 +14868,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5639f8d259ec42b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ac6007295ba42b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14991,7 +15015,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92a93dda4e4b4450"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf968340966754912"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="Rb9e004f631a34147"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R3f466e7fe169444a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R08302848a24e4442"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Rc0730c2bb1374cbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="Rd27f8aec09a1411e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="R84456051bd3141c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R9881050915f742d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R710777ce959d473c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Re4b467c517b44650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Rf45fbf81b87046cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="Rbba7fde3615d432f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="R03fbb11bb1fc4389"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -870,7 +870,7 @@
       </x:c>
       <x:c r="B12" s="28" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành")+COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành có lỗi")</x:f>
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -879,7 +879,7 @@
       </x:c>
       <x:c r="B13" s="29" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Chưa chạy")</x:f>
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1554,7 +1554,7 @@
       </x:c>
       <x:c r="N12" s="36" t="str">
         <x:f>'CRAWL_LOG'!B12</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="O12" s="36" t="str">
         <x:v>Supplementary panel</x:v>
@@ -6252,7 +6252,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9d6dd3fb2ad4d7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra980d0167ee64963"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6870,29 +6870,53 @@
         <x:v>46266</x:v>
       </x:c>
       <x:c r="B12" s="36" t="str">
-        <x:v>Chưa chạy</x:v>
-      </x:c>
-      <x:c r="C12" s="36"/>
-      <x:c r="D12" s="44"/>
-      <x:c r="E12" s="44"/>
-      <x:c r="F12" s="46" t="str">
-        <x:f>IF(OR(D12="",E12=""),"",24*(E12-D12))</x:f>
-      </x:c>
-      <x:c r="G12" s="48"/>
-      <x:c r="H12" s="48"/>
-      <x:c r="I12" s="48"/>
-      <x:c r="J12" s="48"/>
-      <x:c r="K12" s="48"/>
-      <x:c r="L12" s="48"/>
-      <x:c r="M12" s="48"/>
-      <x:c r="N12" s="48"/>
+        <x:v>Hoàn thành có lỗi</x:v>
+      </x:c>
+      <x:c r="C12" s="36" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D12" s="44" t="n">
+        <x:v>46265.73229166667</x:v>
+      </x:c>
+      <x:c r="E12" s="44" t="n">
+        <x:v>46266.582141203704</x:v>
+      </x:c>
+      <x:c r="F12" s="46" t="n">
+        <x:v>20.39638888888889</x:v>
+      </x:c>
+      <x:c r="G12" s="48" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="H12" s="48" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="I12" s="48" t="n">
+        <x:v>1578</x:v>
+      </x:c>
+      <x:c r="J12" s="48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12" s="48" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="L12" s="48" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="M12" s="48" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N12" s="48" t="n">
+        <x:v>15196</x:v>
+      </x:c>
       <x:c r="O12" s="48" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P12" s="36" t="str">
         <x:v>vps</x:v>
       </x:c>
-      <x:c r="Q12" s="36"/>
+      <x:c r="Q12" s="36" t="str">
+        <x:v>Run ID 9; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal API status completed; items pagination 1775; saved_options_count 15196.</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="40" t="n">
@@ -9521,7 +9545,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57fd285de49141ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9aacfcce7f94952"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14655,7 +14679,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R477b4f962e1f4e93"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22d2bc8af7ee4ece"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14868,7 +14892,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ac6007295ba42b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3edcc02865784255"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15015,7 +15039,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf968340966754912"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a364b9c8cc241c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R9881050915f742d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R710777ce959d473c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Re4b467c517b44650"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Rf45fbf81b87046cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="Rbba7fde3615d432f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="R03fbb11bb1fc4389"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R0610662c8b7948fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R01756ab951fa4633"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R48b24c0fc72d411c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Rf7b01ac0591b4423"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R0f81ba785dec4b18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rb4bf76d823414feb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -879,7 +879,7 @@
       </x:c>
       <x:c r="B13" s="29" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Chưa chạy")</x:f>
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1606,7 +1606,7 @@
       </x:c>
       <x:c r="N13" s="37" t="str">
         <x:f>'CRAWL_LOG'!B13</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Đang chạy</x:v>
       </x:c>
       <x:c r="O13" s="37" t="str">
         <x:v>Supplementary panel</x:v>
@@ -6252,7 +6252,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra980d0167ee64963"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fe17fa2137e4443"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6923,10 +6923,14 @@
         <x:v>46267</x:v>
       </x:c>
       <x:c r="B13" s="37" t="str">
-        <x:v>Chưa chạy</x:v>
-      </x:c>
-      <x:c r="C13" s="37"/>
-      <x:c r="D13" s="45"/>
+        <x:v>Đang chạy</x:v>
+      </x:c>
+      <x:c r="C13" s="37" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D13" s="45" t="n">
+        <x:v>46267.02332175926</x:v>
+      </x:c>
       <x:c r="E13" s="45"/>
       <x:c r="F13" s="47" t="str">
         <x:f>IF(OR(D13="",E13=""),"",24*(E13-D13))</x:f>
@@ -6945,7 +6949,9 @@
       <x:c r="P13" s="37" t="str">
         <x:v>vps</x:v>
       </x:c>
-      <x:c r="Q13" s="37"/>
+      <x:c r="Q13" s="37" t="str">
+        <x:v>Scheduled VPS crawl đã tạo trên deploy; artifact không lưu</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="39" t="n">
@@ -9545,7 +9551,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9aacfcce7f94952"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc08a168fc6e34f49"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14679,7 +14685,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22d2bc8af7ee4ece"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re41c081ec56841e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14892,7 +14898,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3edcc02865784255"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49b07e3ba6974b7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15039,7 +15045,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a364b9c8cc241c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabffc1afc72a4e4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R0610662c8b7948fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R01756ab951fa4633"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R48b24c0fc72d411c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Rf7b01ac0591b4423"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R0f81ba785dec4b18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rb4bf76d823414feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R954cc1a13556467e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="Ra42913a6013043e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Re0cf4386e7a64aa7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Rafb1f183f3b74617"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R02791de1d5d94008"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rcc900676f5154fc9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -870,7 +870,7 @@
       </x:c>
       <x:c r="B12" s="28" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành")+COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành có lỗi")</x:f>
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1606,7 +1606,7 @@
       </x:c>
       <x:c r="N13" s="37" t="str">
         <x:f>'CRAWL_LOG'!B13</x:f>
-        <x:v>Đang chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="O13" s="37" t="str">
         <x:v>Supplementary panel</x:v>
@@ -6252,7 +6252,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fe17fa2137e4443"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0dcbdb8d5e340fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6923,7 +6923,7 @@
         <x:v>46267</x:v>
       </x:c>
       <x:c r="B13" s="37" t="str">
-        <x:v>Đang chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="C13" s="37" t="str">
         <x:v>10</x:v>
@@ -6931,18 +6931,37 @@
       <x:c r="D13" s="45" t="n">
         <x:v>46267.02332175926</x:v>
       </x:c>
-      <x:c r="E13" s="45"/>
-      <x:c r="F13" s="47" t="str">
+      <x:c r="E13" s="45" t="n">
+        <x:v>46267.89032407407</x:v>
+      </x:c>
+      <x:c r="F13" s="47" t="n">
         <x:f>IF(OR(D13="",E13=""),"",24*(E13-D13))</x:f>
-      </x:c>
-      <x:c r="G13" s="49"/>
-      <x:c r="H13" s="49"/>
-      <x:c r="I13" s="49"/>
-      <x:c r="J13" s="49"/>
-      <x:c r="K13" s="49"/>
-      <x:c r="L13" s="49"/>
-      <x:c r="M13" s="49"/>
-      <x:c r="N13" s="49"/>
+        <x:v>20.80805555538973</x:v>
+      </x:c>
+      <x:c r="G13" s="49" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="H13" s="49" t="n">
+        <x:v>1775</x:v>
+      </x:c>
+      <x:c r="I13" s="49" t="n">
+        <x:v>1580</x:v>
+      </x:c>
+      <x:c r="J13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="49" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="L13" s="49" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="M13" s="49" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N13" s="49" t="n">
+        <x:v>12932</x:v>
+      </x:c>
       <x:c r="O13" s="49" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -6950,7 +6969,7 @@
         <x:v>vps</x:v>
       </x:c>
       <x:c r="Q13" s="37" t="str">
-        <x:v>Scheduled VPS crawl đã tạo trên deploy; artifact không lưu</x:v>
+        <x:v>Run ID 10; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal API status completed; items pagination 1775; saved_options_count 12932.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -9551,7 +9570,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc08a168fc6e34f49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7857ac9bdda74977"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14685,7 +14704,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re41c081ec56841e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8226eeea3e0140d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14898,7 +14917,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49b07e3ba6974b7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b569f169e4c4959"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15045,7 +15064,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabffc1afc72a4e4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc674762d5ae4847"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R954cc1a13556467e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="Ra42913a6013043e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Re0cf4386e7a64aa7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Rafb1f183f3b74617"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R02791de1d5d94008"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rcc900676f5154fc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R6c360da0a7f0455a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="Rd3e9acc0ffc544ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R64910b0d7104497a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R5aacf9b0e3fa4352"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="Rfc0e994dd8be4e44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rdcd49c344a774af9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -870,7 +870,7 @@
       </x:c>
       <x:c r="B12" s="28" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành")+COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành có lỗi")</x:f>
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -879,7 +879,7 @@
       </x:c>
       <x:c r="B13" s="29" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Chưa chạy")</x:f>
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1658,7 +1658,7 @@
       </x:c>
       <x:c r="N14" s="36" t="str">
         <x:f>'CRAWL_LOG'!B14</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="O14" s="36" t="str">
         <x:v>Supplementary panel</x:v>
@@ -1710,7 +1710,7 @@
       </x:c>
       <x:c r="N15" s="37" t="str">
         <x:f>'CRAWL_LOG'!B15</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Đang chạy</x:v>
       </x:c>
       <x:c r="O15" s="37" t="str">
         <x:v>Supplementary panel</x:v>
@@ -6252,7 +6252,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0dcbdb8d5e340fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2736651819d4ad7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6925,42 +6925,41 @@
       <x:c r="B13" s="37" t="str">
         <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
-      <x:c r="C13" s="37" t="str">
-        <x:v>10</x:v>
+      <x:c r="C13" s="37" t="n">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D13" s="45" t="n">
-        <x:v>46267.02332175926</x:v>
+        <x:v>46267.02444444445</x:v>
       </x:c>
       <x:c r="E13" s="45" t="n">
-        <x:v>46267.89032407407</x:v>
+        <x:v>46267.80280092593</x:v>
       </x:c>
       <x:c r="F13" s="47" t="n">
-        <x:f>IF(OR(D13="",E13=""),"",24*(E13-D13))</x:f>
-        <x:v>20.80805555538973</x:v>
+        <x:v>18.680555555562023</x:v>
       </x:c>
       <x:c r="G13" s="49" t="n">
-        <x:v>1775</x:v>
+        <x:v>1770</x:v>
       </x:c>
       <x:c r="H13" s="49" t="n">
-        <x:v>1775</x:v>
+        <x:v>1770</x:v>
       </x:c>
       <x:c r="I13" s="49" t="n">
-        <x:v>1580</x:v>
+        <x:v>1575</x:v>
       </x:c>
       <x:c r="J13" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K13" s="49" t="n">
-        <x:v>160</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="L13" s="49" t="n">
-        <x:v>30</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M13" s="49" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="N13" s="49" t="n">
-        <x:v>12932</x:v>
+        <x:v>10337</x:v>
       </x:c>
       <x:c r="O13" s="49" t="n">
         <x:v>5</x:v>
@@ -6969,7 +6968,7 @@
         <x:v>vps</x:v>
       </x:c>
       <x:c r="Q13" s="37" t="str">
-        <x:v>Run ID 10; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal API status completed; items pagination 1775; saved_options_count 12932.</x:v>
+        <x:v>Run ID 13; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal API status completed; items pagination 1770; saved_options_count 10337.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -6977,43 +6976,69 @@
         <x:v>46268</x:v>
       </x:c>
       <x:c r="B14" s="36" t="str">
-        <x:v>Chưa chạy</x:v>
-      </x:c>
-      <x:c r="C14" s="36"/>
-      <x:c r="D14" s="44"/>
-      <x:c r="E14" s="44"/>
-      <x:c r="F14" s="46" t="str">
-        <x:f>IF(OR(D14="",E14=""),"",24*(E14-D14))</x:f>
-      </x:c>
-      <x:c r="G14" s="48"/>
-      <x:c r="H14" s="48"/>
-      <x:c r="I14" s="48"/>
-      <x:c r="J14" s="48"/>
-      <x:c r="K14" s="48"/>
-      <x:c r="L14" s="48"/>
-      <x:c r="M14" s="48"/>
-      <x:c r="N14" s="48"/>
+        <x:v>Hoàn thành có lỗi</x:v>
+      </x:c>
+      <x:c r="C14" s="36" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D14" s="44" t="n">
+        <x:v>46267.73277777778</x:v>
+      </x:c>
+      <x:c r="E14" s="44" t="n">
+        <x:v>46268.51113425926</x:v>
+      </x:c>
+      <x:c r="F14" s="46" t="n">
+        <x:v>18.680555555555557</x:v>
+      </x:c>
+      <x:c r="G14" s="48" t="n">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="H14" s="48" t="n">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="I14" s="48" t="n">
+        <x:v>1575</x:v>
+      </x:c>
+      <x:c r="J14" s="48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="48" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="L14" s="48" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="M14" s="48" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N14" s="48" t="n">
+        <x:v>14827</x:v>
+      </x:c>
       <x:c r="O14" s="48" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P14" s="36" t="str">
         <x:v>vps</x:v>
       </x:c>
-      <x:c r="Q14" s="36"/>
+      <x:c r="Q14" s="36" t="str">
+        <x:v>Run ID 13; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal API status completed; items pagination 1770; saved_options_count 14827.</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="40" t="n">
         <x:v>46269</x:v>
       </x:c>
       <x:c r="B15" s="37" t="str">
-        <x:v>Chưa chạy</x:v>
-      </x:c>
-      <x:c r="C15" s="37"/>
-      <x:c r="D15" s="45"/>
+        <x:v>Đang chạy</x:v>
+      </x:c>
+      <x:c r="C15" s="37" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D15" s="45" t="n">
+        <x:v>46268.73201388889</x:v>
+      </x:c>
       <x:c r="E15" s="45"/>
-      <x:c r="F15" s="47" t="str">
-        <x:f>IF(OR(D15="",E15=""),"",24*(E15-D15))</x:f>
-      </x:c>
+      <x:c r="F15" s="47"/>
       <x:c r="G15" s="49"/>
       <x:c r="H15" s="49"/>
       <x:c r="I15" s="49"/>
@@ -7028,7 +7053,9 @@
       <x:c r="P15" s="37" t="str">
         <x:v>vps</x:v>
       </x:c>
-      <x:c r="Q15" s="37"/>
+      <x:c r="Q15" s="37" t="str">
+        <x:v>Scheduled VPS crawl đã tạo trên deploy; artifact không lưu</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="39" t="n">
@@ -9570,7 +9597,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7857ac9bdda74977"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3423fd0f03d64a5b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14704,7 +14731,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8226eeea3e0140d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ec64e853b4642ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14917,7 +14944,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b569f169e4c4959"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3017c6efb7084eff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15064,7 +15091,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc674762d5ae4847"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f9dd5d5840a4b17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R6c360da0a7f0455a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="Rd3e9acc0ffc544ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R64910b0d7104497a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R5aacf9b0e3fa4352"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="Rfc0e994dd8be4e44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rdcd49c344a774af9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="Re70581b677b843ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R5e3b034bc8774328"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R9fb478aa3479445f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R5a3f60c5ee494cbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="Rd5123d728d2d4dc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rd11f3bcbdd7c495d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -845,7 +845,7 @@
         <x:v>Số khách sạn</x:v>
       </x:c>
       <x:c r="B9" s="28" t="n">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -861,7 +861,7 @@
         <x:v>Item dự kiến mỗi ngày</x:v>
       </x:c>
       <x:c r="B11" s="28" t="n">
-        <x:v>1775</x:v>
+        <x:v>1770</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -870,7 +870,7 @@
       </x:c>
       <x:c r="B12" s="28" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành")+COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành có lỗi")</x:f>
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1710,7 +1710,7 @@
       </x:c>
       <x:c r="N15" s="37" t="str">
         <x:f>'CRAWL_LOG'!B15</x:f>
-        <x:v>Đang chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="O15" s="37" t="str">
         <x:v>Supplementary panel</x:v>
@@ -6252,7 +6252,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2736651819d4ad7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2600ce08d8ec436f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6335,7 +6335,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="35" t="str">
-        <x:v>Ghi một dòng cho mỗi crawl date. VPS dùng 355 khách sạn × 5 check-in = 1.775 item dự kiến; không lưu HTML nếu không cần kiểm tra.</x:v>
+        <x:v>Ghi một dòng cho mỗi crawl date. Từ 03/09/2026, VPS dùng 354 khách sạn × 5 check-in = 1.770 item dự kiến; các run cũ giữ số item thực tế; không lưu HTML nếu không cần kiểm tra.</x:v>
       </x:c>
       <x:c r="B2" s="35" t="str">
         <x:v>Ghi một dòng cho mỗi crawl date. VPS dùng 355 khách sạn × 5 check-in = 1.775 item dự kiến; không lưu HTML nếu không cần kiểm tra.</x:v>
@@ -6926,40 +6926,40 @@
         <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="C13" s="37" t="n">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D13" s="45" t="n">
-        <x:v>46267.02444444445</x:v>
+        <x:v>46267.02332175926</x:v>
       </x:c>
       <x:c r="E13" s="45" t="n">
-        <x:v>46267.80280092593</x:v>
+        <x:v>46267.89032407408</x:v>
       </x:c>
       <x:c r="F13" s="47" t="n">
-        <x:v>18.680555555562023</x:v>
+        <x:v>20.8080555556</x:v>
       </x:c>
       <x:c r="G13" s="49" t="n">
-        <x:v>1770</x:v>
+        <x:v>1775</x:v>
       </x:c>
       <x:c r="H13" s="49" t="n">
-        <x:v>1770</x:v>
+        <x:v>1775</x:v>
       </x:c>
       <x:c r="I13" s="49" t="n">
-        <x:v>1575</x:v>
+        <x:v>1580</x:v>
       </x:c>
       <x:c r="J13" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K13" s="49" t="n">
-        <x:v>165</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="L13" s="49" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="M13" s="49" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N13" s="49" t="n">
-        <x:v>10337</x:v>
+        <x:v>12932</x:v>
       </x:c>
       <x:c r="O13" s="49" t="n">
         <x:v>5</x:v>
@@ -6968,7 +6968,7 @@
         <x:v>vps</x:v>
       </x:c>
       <x:c r="Q13" s="37" t="str">
-        <x:v>Run ID 13; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal API status completed; items pagination 1770; saved_options_count 10337.</x:v>
+        <x:v>Run ID 10; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal API status completed; items pagination 1775; saved_options_count 12932.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -6982,13 +6982,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D14" s="44" t="n">
-        <x:v>46267.73277777778</x:v>
+        <x:v>46268.02444444444</x:v>
       </x:c>
       <x:c r="E14" s="44" t="n">
-        <x:v>46268.51113425926</x:v>
+        <x:v>46268.80280092593</x:v>
       </x:c>
       <x:c r="F14" s="46" t="n">
-        <x:v>18.680555555555557</x:v>
+        <x:v>18.6805555556</x:v>
       </x:c>
       <x:c r="G14" s="48" t="n">
         <x:v>1770</x:v>
@@ -7029,24 +7029,44 @@
         <x:v>46269</x:v>
       </x:c>
       <x:c r="B15" s="37" t="str">
-        <x:v>Đang chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="C15" s="37" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D15" s="45" t="n">
-        <x:v>46268.73201388889</x:v>
-      </x:c>
-      <x:c r="E15" s="45"/>
-      <x:c r="F15" s="47"/>
-      <x:c r="G15" s="49"/>
-      <x:c r="H15" s="49"/>
-      <x:c r="I15" s="49"/>
-      <x:c r="J15" s="49"/>
-      <x:c r="K15" s="49"/>
-      <x:c r="L15" s="49"/>
-      <x:c r="M15" s="49"/>
-      <x:c r="N15" s="49"/>
+        <x:v>46269.023680555554</x:v>
+      </x:c>
+      <x:c r="E15" s="45" t="n">
+        <x:v>46269.90994212963</x:v>
+      </x:c>
+      <x:c r="F15" s="47" t="n">
+        <x:v>21.2702777778</x:v>
+      </x:c>
+      <x:c r="G15" s="49" t="n">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="H15" s="49" t="n">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="I15" s="49" t="n">
+        <x:v>1578</x:v>
+      </x:c>
+      <x:c r="J15" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="49" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="L15" s="49" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M15" s="49" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N15" s="49" t="n">
+        <x:v>14967</x:v>
+      </x:c>
       <x:c r="O15" s="49" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -7054,7 +7074,7 @@
         <x:v>vps</x:v>
       </x:c>
       <x:c r="Q15" s="37" t="str">
-        <x:v>Scheduled VPS crawl đã tạo trên deploy; artifact không lưu</x:v>
+        <x:v>Run ID 14; deploy https://hotel.projecthub.io.vn/; artifact off; scraper_version 2.3.0; terminal API status completed; items pagination 1770; saved_options_count 14967.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -9597,7 +9617,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3423fd0f03d64a5b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb38d7f1a24da4aa6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14731,7 +14751,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ec64e853b4642ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf1eadf343c849a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14944,7 +14964,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3017c6efb7084eff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd42d49338ec24d72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15023,7 +15043,7 @@
         <x:v>Upload link_hotel_data_expanded.xlsx</x:v>
       </x:c>
       <x:c r="C6" s="68" t="str">
-        <x:v>355 khách sạn hợp lệ</x:v>
+        <x:v>354 khách sạn hợp lệ</x:v>
       </x:c>
       <x:c r="D6" s="68" t="str">
         <x:v>Dùng cùng file nguồn với local</x:v>
@@ -15051,7 +15071,7 @@
         <x:v>Bắt đầu cào và theo dõi run</x:v>
       </x:c>
       <x:c r="C8" s="68" t="str">
-        <x:v>Khoảng 1.775 item được tạo</x:v>
+        <x:v>Khoảng 1.770 item được tạo</x:v>
       </x:c>
       <x:c r="D8" s="68" t="str">
         <x:v>Không cần lưu HTML nếu chỉ thu thập dataset</x:v>
@@ -15091,7 +15111,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f9dd5d5840a4b17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ab18cf4da97409e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="Re70581b677b843ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R5e3b034bc8774328"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R9fb478aa3479445f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R5a3f60c5ee494cbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="Rd5123d728d2d4dc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rd11f3bcbdd7c495d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R90aa0cd8e47647d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R992edd0fa285454f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R7c3d6f2c7e2d4eb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R552904b42fdf44c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R200edea7866e4799"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="R2cb35b2e34d74e77"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,12 +18,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="5">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="200" formatCode="dd/mm/yyyy"/>
     <x:numFmt numFmtId="201" formatCode="#,##0"/>
     <x:numFmt numFmtId="202" formatCode="0"/>
     <x:numFmt numFmtId="203" formatCode="dd/mm/yyyy hh:mm"/>
     <x:numFmt numFmtId="204" formatCode="0.00"/>
+    <x:numFmt numFmtId="205" formatCode="dd/mm/yyyy hh:mm:ss"/>
   </x:numFmts>
   <x:fonts count="6">
     <x:font>
@@ -208,7 +209,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="71">
+  <x:cellXfs count="72">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -326,6 +327,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="205" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -870,7 +872,7 @@
       </x:c>
       <x:c r="B12" s="28" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành")+COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành có lỗi")</x:f>
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -879,7 +881,7 @@
       </x:c>
       <x:c r="B13" s="29" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Chưa chạy")</x:f>
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1762,7 +1764,7 @@
       </x:c>
       <x:c r="N16" s="36" t="str">
         <x:f>'CRAWL_LOG'!B16</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="O16" s="36" t="str">
         <x:v>Supplementary panel</x:v>
@@ -6252,7 +6254,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2600ce08d8ec436f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3984f84f59b4703"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7082,29 +7084,53 @@
         <x:v>46270</x:v>
       </x:c>
       <x:c r="B16" s="36" t="str">
-        <x:v>Chưa chạy</x:v>
-      </x:c>
-      <x:c r="C16" s="36"/>
-      <x:c r="D16" s="44"/>
-      <x:c r="E16" s="44"/>
-      <x:c r="F16" s="46" t="str">
-        <x:f>IF(OR(D16="",E16=""),"",24*(E16-D16))</x:f>
-      </x:c>
-      <x:c r="G16" s="48"/>
-      <x:c r="H16" s="48"/>
-      <x:c r="I16" s="48"/>
-      <x:c r="J16" s="48"/>
-      <x:c r="K16" s="48"/>
-      <x:c r="L16" s="48"/>
-      <x:c r="M16" s="48"/>
-      <x:c r="N16" s="48"/>
+        <x:v>Hoàn thành có lỗi</x:v>
+      </x:c>
+      <x:c r="C16" s="36" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D16" s="71" t="n">
+        <x:v>46270.0231712963</x:v>
+      </x:c>
+      <x:c r="E16" s="44" t="n">
+        <x:v>46270.93908564815</x:v>
+      </x:c>
+      <x:c r="F16" s="46" t="n">
+        <x:v>21.981944444356486</x:v>
+      </x:c>
+      <x:c r="G16" s="48" t="n">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="H16" s="48" t="n">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="I16" s="48" t="n">
+        <x:v>1583</x:v>
+      </x:c>
+      <x:c r="J16" s="48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="48" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="L16" s="48" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M16" s="48" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N16" s="48" t="n">
+        <x:v>14706</x:v>
+      </x:c>
       <x:c r="O16" s="48" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P16" s="36" t="str">
         <x:v>vps</x:v>
       </x:c>
-      <x:c r="Q16" s="36"/>
+      <x:c r="Q16" s="36" t="str">
+        <x:v>Run ID 15; deploy https://hotel.projecthub.io.vn/; artifact không lưu; scraper_version 2.3.0; terminal API status completed; items pagination 1770; saved_options_count 14706.</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="40" t="n">
@@ -9617,7 +9643,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb38d7f1a24da4aa6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R978870dbcdca4fd2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14751,7 +14777,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf1eadf343c849a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06f786ee14f84fcb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14964,7 +14990,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd42d49338ec24d72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re24dce093d5b4ff8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15111,7 +15137,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ab18cf4da97409e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b46bf4fab604294"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="Rdb109da4460443c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R76387ac929da4e74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Rd9b627334e4e46d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R6280329e24524b29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R2d165f13324e4815"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Rbc0a0afc3c384adf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R334190919a9b4191"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R8b0b6d2b1c35439c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Readaa929ae354ffd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R567bb33dc7b54542"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R50ea720fbca14fba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="R1d1f87b967ad48bd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -996,7 +996,7 @@
       </x:c>
       <x:c r="B13" s="75" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Chưa chạy")</x:f>
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2085,7 +2085,7 @@
       </x:c>
       <x:c r="N19" s="37" t="str">
         <x:f>'CRAWL_LOG'!B19</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Đang chạy</x:v>
       </x:c>
       <x:c r="O19" s="37" t="inlineStr">
         <x:is>
@@ -7085,7 +7085,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38e036c63fed4b5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d4e4f9dde034673"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8117,13 +8117,15 @@
       <x:c r="A19" s="79" t="n">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="B19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chưa chạy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" s="37" t="n"/>
-      <x:c r="D19" s="84" t="n"/>
+      <x:c r="B19" s="37" t="str">
+        <x:v>Đang chạy</x:v>
+      </x:c>
+      <x:c r="C19" s="37" t="str">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D19" s="84" t="n">
+        <x:v>46273.02431712963</x:v>
+      </x:c>
       <x:c r="E19" s="84" t="n"/>
       <x:c r="F19" s="85" t="str">
         <x:f>IF(OR(D19="",E19=""),"",24*(E19-D19))</x:f>
@@ -8139,12 +8141,12 @@
       <x:c r="O19" s="86" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P19" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">vps</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q19" s="37" t="n"/>
+      <x:c r="P19" s="37" t="str">
+        <x:v>vps</x:v>
+      </x:c>
+      <x:c r="Q19" s="37" t="str">
+        <x:v>Scheduled VPS crawl đã tạo trên deploy; artifact không lưu</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="76" t="n">
@@ -10902,7 +10904,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96f44c42e7774e96"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c48ecdc5a3449b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16576,7 +16578,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d9fd59f01a646cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabdf69b747974a95"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16866,7 +16868,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb9fce0835094de4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9898746c6ccb48d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17056,7 +17058,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47960824bd2b4e9b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08c2913ac9114aaf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R334190919a9b4191"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="R8b0b6d2b1c35439c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="Readaa929ae354ffd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R567bb33dc7b54542"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R50ea720fbca14fba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="R1d1f87b967ad48bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="Rf631b05d1b5941bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="Rf9b9201294154f65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R3f7f49e745e0482b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R51ee3179bd574fd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="Rbe749ec118974481"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Re45acd104b3f406d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -985,7 +985,7 @@
       </x:c>
       <x:c r="B12" s="74" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành")+COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành có lỗi")</x:f>
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -996,7 +996,7 @@
       </x:c>
       <x:c r="B13" s="75" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Chưa chạy")</x:f>
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2145,7 +2145,7 @@
       </x:c>
       <x:c r="N20" s="36" t="str">
         <x:f>'CRAWL_LOG'!B20</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="O20" s="36" t="inlineStr">
         <x:is>
@@ -7085,7 +7085,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d4e4f9dde034673"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc447ae44a6c34a0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8152,34 +8152,54 @@
       <x:c r="A20" s="76" t="n">
         <x:v>46274</x:v>
       </x:c>
-      <x:c r="B20" s="36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chưa chạy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C20" s="36" t="n"/>
-      <x:c r="D20" s="81" t="n"/>
-      <x:c r="E20" s="81" t="n"/>
-      <x:c r="F20" s="82" t="str">
-        <x:f>IF(OR(D20="",E20=""),"",24*(E20-D20))</x:f>
-      </x:c>
-      <x:c r="G20" s="83" t="n"/>
-      <x:c r="H20" s="83" t="n"/>
-      <x:c r="I20" s="83" t="n"/>
-      <x:c r="J20" s="83" t="n"/>
-      <x:c r="K20" s="83" t="n"/>
-      <x:c r="L20" s="83" t="n"/>
-      <x:c r="M20" s="83" t="n"/>
-      <x:c r="N20" s="83" t="n"/>
+      <x:c r="B20" s="36" t="str">
+        <x:v>Hoàn thành có lỗi</x:v>
+      </x:c>
+      <x:c r="C20" s="36" t="str">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D20" s="81" t="n">
+        <x:v>46274.02339120371</x:v>
+      </x:c>
+      <x:c r="E20" s="81" t="n">
+        <x:v>46274.92560185185</x:v>
+      </x:c>
+      <x:c r="F20" s="82" t="n">
+        <x:v>21.653055555555557</x:v>
+      </x:c>
+      <x:c r="G20" s="83" t="n">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="H20" s="83" t="n">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="I20" s="83" t="n">
+        <x:v>1574</x:v>
+      </x:c>
+      <x:c r="J20" s="83" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K20" s="83" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="L20" s="83" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="M20" s="83" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N20" s="83" t="n">
+        <x:v>15038</x:v>
+      </x:c>
       <x:c r="O20" s="83" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P20" s="36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">vps</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q20" s="36" t="n"/>
+      <x:c r="P20" s="36" t="str">
+        <x:v>vps</x:v>
+      </x:c>
+      <x:c r="Q20" s="36" t="str">
+        <x:v>Run ID 19; deploy https://hotel.projecthub.io.vn/; artifact không lưu; scraper_version 2.3.0; terminal API status completed; items pagination 1770; saved_options_count 15038.</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="79" t="n">
@@ -10904,7 +10924,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c48ecdc5a3449b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51a68b3337454f99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16578,7 +16598,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabdf69b747974a95"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d134c63474146dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16868,7 +16888,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9898746c6ccb48d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R113122d8bbc647bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17058,7 +17078,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08c2913ac9114aaf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d284580d01847c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="Rf631b05d1b5941bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="Rf9b9201294154f65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R3f7f49e745e0482b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="R51ee3179bd574fd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="Rbe749ec118974481"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="Re45acd104b3f406d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" r:id="R0134f69655cd4251"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS_CRAWL_PLAN" sheetId="2" r:id="Rb9b858c4d0554c5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRAWL_LOG" sheetId="3" r:id="R9eb7df5d11304338"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOCAL_REFERENCE" sheetId="4" r:id="Rb11701ee62564df7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLOT_RULES" sheetId="5" r:id="R169e1106756d43bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" r:id="R63535ae75dad42b4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -207,7 +207,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="89">
+  <x:cellXfs count="91">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -343,6 +343,8 @@
     <x:xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0"/>
     <x:xf numFmtId="166" fontId="0" fillId="6" borderId="0" xfId="0"/>
     <x:xf numFmtId="167" fontId="0" fillId="6" borderId="0" xfId="0"/>
+    <x:xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -985,7 +987,7 @@
       </x:c>
       <x:c r="B12" s="74" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành")+COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Hoàn thành có lỗi")</x:f>
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -996,7 +998,7 @@
       </x:c>
       <x:c r="B13" s="75" t="n">
         <x:f>COUNTIF('CRAWL_LOG'!$B$4:$B$102,"Chưa chạy")</x:f>
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2085,7 +2087,7 @@
       </x:c>
       <x:c r="N19" s="37" t="str">
         <x:f>'CRAWL_LOG'!B19</x:f>
-        <x:v>Đang chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="O19" s="37" t="inlineStr">
         <x:is>
@@ -2205,7 +2207,7 @@
       </x:c>
       <x:c r="N21" s="37" t="str">
         <x:f>'CRAWL_LOG'!B21</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="O21" s="37" t="inlineStr">
         <x:is>
@@ -2265,7 +2267,7 @@
       </x:c>
       <x:c r="N22" s="36" t="str">
         <x:f>'CRAWL_LOG'!B22</x:f>
-        <x:v>Chưa chạy</x:v>
+        <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
       <x:c r="O22" s="36" t="inlineStr">
         <x:is>
@@ -7085,7 +7087,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc447ae44a6c34a0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc48d196ad384300"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8069,16 +8071,18 @@
       <x:c r="B18" s="36" t="str">
         <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
-      <x:c r="C18" s="36" t="str">
+      <x:c r="C18" s="36" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D18" s="88" t="n">
-        <x:v>46272.02332175926</x:v>
-      </x:c>
-      <x:c r="E18" s="81" t="n">
+      <x:c r="D18" s="89" t="n">
+        <x:v>46272.02271990741</x:v>
+      </x:c>
+      <x:c r="E18" s="89" t="n">
         <x:v>46272.93084490741</x:v>
       </x:c>
-      <x:c r="F18" s="82"/>
+      <x:c r="F18" s="82" t="n">
+        <x:v>21.795</x:v>
+      </x:c>
       <x:c r="G18" s="83" t="n">
         <x:v>1770</x:v>
       </x:c>
@@ -8110,7 +8114,7 @@
         <x:v>vps</x:v>
       </x:c>
       <x:c r="Q18" s="36" t="str">
-        <x:v>Run ID 17; deploy https://hotel.projecthub.io.vn/; artifact không lưu; scraper_version 2.3.0; terminal API status completed; items pagination 1770; saved_options_count 14688.</x:v>
+        <x:v>Run ID 17; deploy https://hotel.projecthub.io.vn/; artifact không lưu; scraper_version=2.3.0</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -8118,26 +8122,44 @@
         <x:v>46273</x:v>
       </x:c>
       <x:c r="B19" s="37" t="str">
-        <x:v>Đang chạy</x:v>
-      </x:c>
-      <x:c r="C19" s="37" t="str">
+        <x:v>Hoàn thành có lỗi</x:v>
+      </x:c>
+      <x:c r="C19" s="37" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D19" s="84" t="n">
+      <x:c r="D19" s="90" t="n">
         <x:v>46273.02431712963</x:v>
       </x:c>
-      <x:c r="E19" s="84" t="n"/>
-      <x:c r="F19" s="85" t="str">
-        <x:f>IF(OR(D19="",E19=""),"",24*(E19-D19))</x:f>
-      </x:c>
-      <x:c r="G19" s="86" t="n"/>
-      <x:c r="H19" s="86" t="n"/>
-      <x:c r="I19" s="86" t="n"/>
-      <x:c r="J19" s="86" t="n"/>
-      <x:c r="K19" s="86" t="n"/>
-      <x:c r="L19" s="86" t="n"/>
-      <x:c r="M19" s="86" t="n"/>
-      <x:c r="N19" s="86" t="n"/>
+      <x:c r="E19" s="90" t="n">
+        <x:v>46273.966412037036</x:v>
+      </x:c>
+      <x:c r="F19" s="85" t="n">
+        <x:v>22.610277777777778</x:v>
+      </x:c>
+      <x:c r="G19" s="86" t="n">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="H19" s="86" t="n">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="I19" s="86" t="n">
+        <x:v>1582</x:v>
+      </x:c>
+      <x:c r="J19" s="86" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19" s="86" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="L19" s="86" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="M19" s="86" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N19" s="86" t="n">
+        <x:v>15259</x:v>
+      </x:c>
       <x:c r="O19" s="86" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -8145,7 +8167,7 @@
         <x:v>vps</x:v>
       </x:c>
       <x:c r="Q19" s="37" t="str">
-        <x:v>Scheduled VPS crawl đã tạo trên deploy; artifact không lưu</x:v>
+        <x:v>Run ID 18; deploy https://hotel.projecthub.io.vn/; artifact không lưu; scraper_version=2.3.0</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -8155,13 +8177,13 @@
       <x:c r="B20" s="36" t="str">
         <x:v>Hoàn thành có lỗi</x:v>
       </x:c>
-      <x:c r="C20" s="36" t="str">
+      <x:c r="C20" s="36" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D20" s="81" t="n">
+      <x:c r="D20" s="89" t="n">
         <x:v>46274.02339120371</x:v>
       </x:c>
-      <x:c r="E20" s="81" t="n">
+      <x:c r="E20" s="89" t="n">
         <x:v>46274.92560185185</x:v>
       </x:c>
       <x:c r="F20" s="82" t="n">
@@ -8198,74 +8220,114 @@
         <x:v>vps</x:v>
       </x:c>
       <x:c r="Q20" s="36" t="str">
-        <x:v>Run ID 19; deploy https://hotel.projecthub.io.vn/; artifact không lưu; scraper_version 2.3.0; terminal API status completed; items pagination 1770; saved_options_count 15038.</x:v>
+        <x:v>Run ID 19; deploy https://hotel.projecthub.io.vn/; artifact không lưu; scraper_version=2.3.0</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="79" t="n">
         <x:v>46275</x:v>
       </x:c>
-      <x:c r="B21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chưa chạy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C21" s="37" t="n"/>
-      <x:c r="D21" s="84" t="n"/>
-      <x:c r="E21" s="84" t="n"/>
-      <x:c r="F21" s="85" t="str">
-        <x:f>IF(OR(D21="",E21=""),"",24*(E21-D21))</x:f>
-      </x:c>
-      <x:c r="G21" s="86" t="n"/>
-      <x:c r="H21" s="86" t="n"/>
-      <x:c r="I21" s="86" t="n"/>
-      <x:c r="J21" s="86" t="n"/>
-      <x:c r="K21" s="86" t="n"/>
-      <x:c r="L21" s="86" t="n"/>
-      <x:c r="M21" s="86" t="n"/>
-      <x:c r="N21" s="86" t="n"/>
+      <x:c r="B21" s="37" t="str">
+        <x:v>Hoàn thành có lỗi</x:v>
+      </x:c>
+      <x:c r="C21" s="37" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D21" s="90" t="n">
+        <x:v>46275.029953703706</x:v>
+      </x:c>
+      <x:c r="E21" s="90" t="n">
+        <x:v>46275.94020833333</x:v>
+      </x:c>
+      <x:c r="F21" s="85" t="n">
+        <x:v>21.84611111111111</x:v>
+      </x:c>
+      <x:c r="G21" s="86" t="n">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="H21" s="86" t="n">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="I21" s="86" t="n">
+        <x:v>1569</x:v>
+      </x:c>
+      <x:c r="J21" s="86" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K21" s="86" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="L21" s="86" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M21" s="86" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N21" s="86" t="n">
+        <x:v>14673</x:v>
+      </x:c>
       <x:c r="O21" s="86" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P21" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">vps</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q21" s="37" t="n"/>
+      <x:c r="P21" s="37" t="str">
+        <x:v>vps</x:v>
+      </x:c>
+      <x:c r="Q21" s="37" t="str">
+        <x:v>Run ID 20; deploy https://hotel.projecthub.io.vn/; artifact không lưu; scraper_version=2.3.0</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="76" t="n">
         <x:v>46276</x:v>
       </x:c>
-      <x:c r="B22" s="36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chưa chạy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C22" s="36" t="n"/>
-      <x:c r="D22" s="81" t="n"/>
-      <x:c r="E22" s="81" t="n"/>
-      <x:c r="F22" s="82" t="str">
-        <x:f>IF(OR(D22="",E22=""),"",24*(E22-D22))</x:f>
-      </x:c>
-      <x:c r="G22" s="83" t="n"/>
-      <x:c r="H22" s="83" t="n"/>
-      <x:c r="I22" s="83" t="n"/>
-      <x:c r="J22" s="83" t="n"/>
-      <x:c r="K22" s="83" t="n"/>
-      <x:c r="L22" s="83" t="n"/>
-      <x:c r="M22" s="83" t="n"/>
-      <x:c r="N22" s="83" t="n"/>
+      <x:c r="B22" s="36" t="str">
+        <x:v>Hoàn thành có lỗi</x:v>
+      </x:c>
+      <x:c r="C22" s="36" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D22" s="89" t="n">
+        <x:v>46276.025868055556</x:v>
+      </x:c>
+      <x:c r="E22" s="89" t="n">
+        <x:v>46276.94533564815</x:v>
+      </x:c>
+      <x:c r="F22" s="82" t="n">
+        <x:v>22.067222222222224</x:v>
+      </x:c>
+      <x:c r="G22" s="83" t="n">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="H22" s="83" t="n">
+        <x:v>1770</x:v>
+      </x:c>
+      <x:c r="I22" s="83" t="n">
+        <x:v>1579</x:v>
+      </x:c>
+      <x:c r="J22" s="83" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K22" s="83" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="L22" s="83" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M22" s="83" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N22" s="83" t="n">
+        <x:v>14887</x:v>
+      </x:c>
       <x:c r="O22" s="83" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P22" s="36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">vps</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q22" s="36" t="n"/>
+      <x:c r="P22" s="36" t="str">
+        <x:v>vps</x:v>
+      </x:c>
+      <x:c r="Q22" s="36" t="str">
+        <x:v>Run ID 21; deploy https://hotel.projecthub.io.vn/; artifact không lưu; scraper_version=2.3.0</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="79" t="n">
@@ -10924,7 +10986,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51a68b3337454f99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6826d5704d234ffe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16598,7 +16660,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d134c63474146dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R410c282a5d544b2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16888,7 +16950,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R113122d8bbc647bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd22c4ca0fb94900"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17078,7 +17140,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d284580d01847c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40c36dbf13c04b6b"/>
   </x:tableParts>
 </x:worksheet>
 </file>